--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428439</v>
+        <v>125428384</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578198</v>
+        <v>578310</v>
       </c>
       <c r="R2" t="n">
-        <v>7084409</v>
+        <v>7084391</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125434424</v>
+        <v>125434406</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578129</v>
+        <v>578054</v>
       </c>
       <c r="R3" t="n">
-        <v>7084335</v>
+        <v>7084281</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125434423</v>
+        <v>125428435</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578129</v>
+        <v>577974</v>
       </c>
       <c r="R4" t="n">
-        <v>7084328</v>
+        <v>7084344</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428403</v>
+        <v>125428401</v>
       </c>
       <c r="B5" t="n">
         <v>78546</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578219</v>
+        <v>577984</v>
       </c>
       <c r="R5" t="n">
-        <v>7084292</v>
+        <v>7084342</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428409</v>
+        <v>125428439</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578221</v>
+        <v>578198</v>
       </c>
       <c r="R6" t="n">
-        <v>7084280</v>
+        <v>7084409</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428355</v>
+        <v>125428349</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577852</v>
+        <v>578141</v>
       </c>
       <c r="R7" t="n">
-        <v>7084241</v>
+        <v>7084345</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125434411</v>
+        <v>125428422</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,38 +1299,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578199</v>
+        <v>577974</v>
       </c>
       <c r="R8" t="n">
-        <v>7084408</v>
+        <v>7084348</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1381,22 +1381,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428393</v>
+        <v>125428365</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5467</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578033</v>
+        <v>577840</v>
       </c>
       <c r="R9" t="n">
-        <v>7084326</v>
+        <v>7084230</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428440</v>
+        <v>125434411</v>
       </c>
       <c r="B10" t="n">
         <v>78546</v>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578180</v>
+        <v>578199</v>
       </c>
       <c r="R10" t="n">
-        <v>7084369</v>
+        <v>7084408</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1585,22 +1585,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428435</v>
+        <v>125428403</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,25 +1609,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577974</v>
+        <v>578219</v>
       </c>
       <c r="R11" t="n">
-        <v>7084344</v>
+        <v>7084292</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428381</v>
+        <v>125428437</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578011</v>
+        <v>578117</v>
       </c>
       <c r="R12" t="n">
-        <v>7084346</v>
+        <v>7084345</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,6 +1783,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1801,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125434420</v>
+        <v>125428380</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578025</v>
+        <v>577982</v>
       </c>
       <c r="R13" t="n">
-        <v>7084331</v>
+        <v>7084332</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,28 +1886,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125434406</v>
+        <v>125428407</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,38 +1917,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578054</v>
+        <v>578118</v>
       </c>
       <c r="R14" t="n">
-        <v>7084281</v>
+        <v>7084300</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1993,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428359</v>
+        <v>125428423</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,38 +2023,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578081</v>
+        <v>577989</v>
       </c>
       <c r="R15" t="n">
-        <v>7084315</v>
+        <v>7084344</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2107,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428365</v>
+        <v>125434410</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577840</v>
+        <v>578022</v>
       </c>
       <c r="R16" t="n">
-        <v>7084230</v>
+        <v>7084327</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2197,22 +2207,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428433</v>
+        <v>125434421</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578080</v>
+        <v>578083</v>
       </c>
       <c r="R17" t="n">
-        <v>7084336</v>
+        <v>7084291</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2299,22 +2309,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428422</v>
+        <v>125428440</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,42 +2333,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577974</v>
+        <v>578180</v>
       </c>
       <c r="R18" t="n">
-        <v>7084348</v>
+        <v>7084369</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2417,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125434421</v>
+        <v>125428386</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2433,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2457,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578083</v>
+        <v>578323</v>
       </c>
       <c r="R19" t="n">
-        <v>7084291</v>
+        <v>7084369</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2507,12 +2513,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2621,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428423</v>
+        <v>125428424</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2633,30 +2639,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2665,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577989</v>
+        <v>578119</v>
       </c>
       <c r="R21" t="n">
-        <v>7084344</v>
+        <v>7084345</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125434408</v>
+        <v>125428359</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577968</v>
+        <v>578081</v>
       </c>
       <c r="R22" t="n">
-        <v>7084350</v>
+        <v>7084315</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,22 +2824,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428358</v>
+        <v>125428381</v>
       </c>
       <c r="B23" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2845,21 +2852,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2869,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578013</v>
+        <v>578011</v>
       </c>
       <c r="R23" t="n">
-        <v>7084338</v>
+        <v>7084346</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2931,10 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428349</v>
+        <v>125428393</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>91476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2947,21 +2954,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2971,10 +2978,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578141</v>
+        <v>578033</v>
       </c>
       <c r="R24" t="n">
-        <v>7084345</v>
+        <v>7084326</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3033,10 +3040,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428437</v>
+        <v>125428438</v>
       </c>
       <c r="B25" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,34 +3056,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578117</v>
+        <v>578202</v>
       </c>
       <c r="R25" t="n">
-        <v>7084345</v>
+        <v>7084386</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3111,13 +3123,17 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428407</v>
+        <v>125428355</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,42 +3164,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578118</v>
+        <v>577852</v>
       </c>
       <c r="R26" t="n">
-        <v>7084300</v>
+        <v>7084241</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428427</v>
+        <v>125428352</v>
       </c>
       <c r="B27" t="n">
-        <v>91172</v>
+        <v>79428</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,25 +3266,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3282,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577975</v>
+        <v>578226</v>
       </c>
       <c r="R27" t="n">
-        <v>7084314</v>
+        <v>7084292</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3344,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428401</v>
+        <v>125428426</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>91172</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3356,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3384,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577984</v>
+        <v>577942</v>
       </c>
       <c r="R28" t="n">
-        <v>7084342</v>
+        <v>7084344</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3446,10 +3458,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428424</v>
+        <v>125428402</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3462,39 +3474,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578119</v>
+        <v>578297</v>
       </c>
       <c r="R29" t="n">
-        <v>7084345</v>
+        <v>7084334</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3553,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428380</v>
+        <v>125434408</v>
       </c>
       <c r="B30" t="n">
-        <v>79919</v>
+        <v>78546</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3565,25 +3572,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3593,10 +3600,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577982</v>
+        <v>577968</v>
       </c>
       <c r="R30" t="n">
-        <v>7084332</v>
+        <v>7084350</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3637,29 +3644,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428438</v>
+        <v>125428400</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3672,39 +3678,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578202</v>
+        <v>577946</v>
       </c>
       <c r="R31" t="n">
-        <v>7084386</v>
+        <v>7084330</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3737,11 +3738,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,10 +3764,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428426</v>
+        <v>125434422</v>
       </c>
       <c r="B32" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3780,25 +3776,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3804,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577942</v>
+        <v>578121</v>
       </c>
       <c r="R32" t="n">
-        <v>7084344</v>
+        <v>7084311</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3858,22 +3854,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434422</v>
+        <v>125428433</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3882,25 +3878,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3910,10 +3906,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578121</v>
+        <v>578080</v>
       </c>
       <c r="R33" t="n">
-        <v>7084311</v>
+        <v>7084336</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,22 +3956,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428410</v>
+        <v>125428358</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3984,42 +3980,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578214</v>
+        <v>578013</v>
       </c>
       <c r="R34" t="n">
-        <v>7084276</v>
+        <v>7084338</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,10 +4172,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428384</v>
+        <v>125428409</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4192,38 +4184,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578310</v>
+        <v>578221</v>
       </c>
       <c r="R36" t="n">
-        <v>7084391</v>
+        <v>7084280</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4282,10 +4278,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428386</v>
+        <v>125434420</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4298,21 +4294,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578323</v>
+        <v>578025</v>
       </c>
       <c r="R37" t="n">
-        <v>7084369</v>
+        <v>7084331</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4372,22 +4368,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428352</v>
+        <v>125434424</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4400,21 +4396,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4424,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578226</v>
+        <v>578129</v>
       </c>
       <c r="R38" t="n">
-        <v>7084292</v>
+        <v>7084335</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4474,22 +4470,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125434410</v>
+        <v>125428427</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>91172</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,25 +4494,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4526,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578022</v>
+        <v>577975</v>
       </c>
       <c r="R39" t="n">
-        <v>7084327</v>
+        <v>7084314</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4576,15 +4572,223 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125434423</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>578129</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7084328</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Michaela Ehmann</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Michaela Ehmann</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125428410</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>578214</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7084276</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428384</v>
+        <v>125434411</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578310</v>
+        <v>578199</v>
       </c>
       <c r="R2" t="n">
-        <v>7084391</v>
+        <v>7084408</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125434406</v>
+        <v>125434422</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578054</v>
+        <v>578121</v>
       </c>
       <c r="R3" t="n">
-        <v>7084281</v>
+        <v>7084311</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428435</v>
+        <v>125428384</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577974</v>
+        <v>578310</v>
       </c>
       <c r="R4" t="n">
-        <v>7084344</v>
+        <v>7084391</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428401</v>
+        <v>125428422</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577984</v>
+        <v>577974</v>
       </c>
       <c r="R5" t="n">
-        <v>7084342</v>
+        <v>7084348</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428439</v>
+        <v>125428386</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578198</v>
+        <v>578323</v>
       </c>
       <c r="R6" t="n">
-        <v>7084409</v>
+        <v>7084369</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428349</v>
+        <v>125428424</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>56828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,31 +1205,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578141</v>
+        <v>578119</v>
       </c>
       <c r="R7" t="n">
         <v>7084345</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428422</v>
+        <v>125428381</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,42 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577974</v>
+        <v>578011</v>
       </c>
       <c r="R8" t="n">
-        <v>7084348</v>
+        <v>7084346</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428365</v>
+        <v>125428359</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>79565</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577840</v>
+        <v>578081</v>
       </c>
       <c r="R9" t="n">
-        <v>7084230</v>
+        <v>7084315</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125434411</v>
+        <v>125428440</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578199</v>
+        <v>578180</v>
       </c>
       <c r="R10" t="n">
-        <v>7084408</v>
+        <v>7084369</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1585,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428403</v>
+        <v>125434421</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578219</v>
+        <v>578083</v>
       </c>
       <c r="R11" t="n">
-        <v>7084292</v>
+        <v>7084291</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1687,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428437</v>
+        <v>125428433</v>
       </c>
       <c r="B12" t="n">
-        <v>78194</v>
+        <v>92448</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578117</v>
+        <v>578080</v>
       </c>
       <c r="R12" t="n">
-        <v>7084345</v>
+        <v>7084336</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1802,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428380</v>
+        <v>125434420</v>
       </c>
       <c r="B13" t="n">
-        <v>79919</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577982</v>
+        <v>578025</v>
       </c>
       <c r="R13" t="n">
-        <v>7084332</v>
+        <v>7084331</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1886,29 +1890,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428407</v>
+        <v>125434423</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,42 +1920,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578118</v>
+        <v>578129</v>
       </c>
       <c r="R14" t="n">
-        <v>7084300</v>
+        <v>7084328</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1999,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428423</v>
+        <v>125428427</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,38 +2026,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577989</v>
+        <v>577975</v>
       </c>
       <c r="R15" t="n">
-        <v>7084344</v>
+        <v>7084314</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125434410</v>
+        <v>125428409</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,38 +2124,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578022</v>
+        <v>578221</v>
       </c>
       <c r="R16" t="n">
-        <v>7084327</v>
+        <v>7084280</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2207,22 +2206,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125434421</v>
+        <v>125428439</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2234,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578083</v>
+        <v>578198</v>
       </c>
       <c r="R17" t="n">
-        <v>7084291</v>
+        <v>7084409</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2309,22 +2308,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428440</v>
+        <v>125428435</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>92448</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2332,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578180</v>
+        <v>577974</v>
       </c>
       <c r="R18" t="n">
-        <v>7084369</v>
+        <v>7084344</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428386</v>
+        <v>125428438</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,34 +2438,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578323</v>
+        <v>578202</v>
       </c>
       <c r="R19" t="n">
-        <v>7084369</v>
+        <v>7084386</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2499,6 +2503,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125434407</v>
+        <v>125428401</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577930</v>
+        <v>577984</v>
       </c>
       <c r="R20" t="n">
-        <v>7084334</v>
+        <v>7084342</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2615,22 +2624,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428424</v>
+        <v>125428423</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,31 +2648,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2672,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578119</v>
+        <v>577989</v>
       </c>
       <c r="R21" t="n">
-        <v>7084345</v>
+        <v>7084344</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,10 +2742,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428359</v>
+        <v>125428349</v>
       </c>
       <c r="B22" t="n">
-        <v>79428</v>
+        <v>75025</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578081</v>
+        <v>578141</v>
       </c>
       <c r="R22" t="n">
-        <v>7084315</v>
+        <v>7084345</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2836,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428381</v>
+        <v>125434424</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2852,21 +2860,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578011</v>
+        <v>578129</v>
       </c>
       <c r="R23" t="n">
-        <v>7084346</v>
+        <v>7084335</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2926,22 +2934,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428393</v>
+        <v>125428437</v>
       </c>
       <c r="B24" t="n">
-        <v>91476</v>
+        <v>78331</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2954,21 +2962,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5467</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2978,10 +2986,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578033</v>
+        <v>578117</v>
       </c>
       <c r="R24" t="n">
-        <v>7084326</v>
+        <v>7084345</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3022,6 +3030,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3040,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428438</v>
+        <v>125434406</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3056,39 +3065,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578202</v>
+        <v>578054</v>
       </c>
       <c r="R25" t="n">
-        <v>7084386</v>
+        <v>7084281</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,11 +3127,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3140,22 +3139,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428355</v>
+        <v>125428407</v>
       </c>
       <c r="B26" t="n">
-        <v>79428</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,38 +3163,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577852</v>
+        <v>578118</v>
       </c>
       <c r="R26" t="n">
-        <v>7084241</v>
+        <v>7084300</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3254,10 +3257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428352</v>
+        <v>125428391</v>
       </c>
       <c r="B27" t="n">
-        <v>79428</v>
+        <v>80064</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3269,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3297,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578226</v>
+        <v>578310</v>
       </c>
       <c r="R27" t="n">
-        <v>7084292</v>
+        <v>7084392</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3356,10 +3359,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428426</v>
+        <v>125428410</v>
       </c>
       <c r="B28" t="n">
-        <v>91172</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,34 +3375,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577942</v>
+        <v>578214</v>
       </c>
       <c r="R28" t="n">
-        <v>7084344</v>
+        <v>7084276</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3458,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428402</v>
+        <v>125428426</v>
       </c>
       <c r="B29" t="n">
-        <v>78546</v>
+        <v>91326</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,25 +3477,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578297</v>
+        <v>577942</v>
       </c>
       <c r="R29" t="n">
-        <v>7084334</v>
+        <v>7084344</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3560,10 +3567,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125434408</v>
+        <v>125428403</v>
       </c>
       <c r="B30" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577968</v>
+        <v>578219</v>
       </c>
       <c r="R30" t="n">
-        <v>7084350</v>
+        <v>7084292</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3650,22 +3657,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428400</v>
+        <v>125428365</v>
       </c>
       <c r="B31" t="n">
-        <v>78546</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3678,21 +3685,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3702,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577946</v>
+        <v>577840</v>
       </c>
       <c r="R31" t="n">
-        <v>7084330</v>
+        <v>7084230</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3764,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434422</v>
+        <v>125434410</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3780,21 +3787,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3804,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578121</v>
+        <v>578022</v>
       </c>
       <c r="R32" t="n">
-        <v>7084311</v>
+        <v>7084327</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3866,10 +3873,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428433</v>
+        <v>125428358</v>
       </c>
       <c r="B33" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,25 +3885,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3906,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578080</v>
+        <v>578013</v>
       </c>
       <c r="R33" t="n">
-        <v>7084336</v>
+        <v>7084338</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3968,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428358</v>
+        <v>125428355</v>
       </c>
       <c r="B34" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4008,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578013</v>
+        <v>577852</v>
       </c>
       <c r="R34" t="n">
-        <v>7084338</v>
+        <v>7084241</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4070,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428391</v>
+        <v>125428393</v>
       </c>
       <c r="B35" t="n">
-        <v>79927</v>
+        <v>91636</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,25 +4089,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>5467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4110,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578310</v>
+        <v>578033</v>
       </c>
       <c r="R35" t="n">
-        <v>7084392</v>
+        <v>7084326</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4172,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428409</v>
+        <v>125434407</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78683</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,42 +4191,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578221</v>
+        <v>577930</v>
       </c>
       <c r="R36" t="n">
-        <v>7084280</v>
+        <v>7084334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4266,22 +4269,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125434420</v>
+        <v>125428352</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79565</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,21 +4297,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578025</v>
+        <v>578226</v>
       </c>
       <c r="R37" t="n">
-        <v>7084331</v>
+        <v>7084292</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4368,22 +4371,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125434424</v>
+        <v>125428402</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,21 +4399,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578129</v>
+        <v>578297</v>
       </c>
       <c r="R38" t="n">
-        <v>7084335</v>
+        <v>7084334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4470,22 +4473,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428427</v>
+        <v>125428380</v>
       </c>
       <c r="B39" t="n">
-        <v>91172</v>
+        <v>80056</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,25 +4497,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4522,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577975</v>
+        <v>577982</v>
       </c>
       <c r="R39" t="n">
-        <v>7084314</v>
+        <v>7084332</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4566,6 +4569,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4584,10 +4588,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125434423</v>
+        <v>125434408</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4600,21 +4604,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4624,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578129</v>
+        <v>577968</v>
       </c>
       <c r="R40" t="n">
-        <v>7084328</v>
+        <v>7084350</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4686,10 +4690,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428410</v>
+        <v>125428400</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78683</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4698,42 +4702,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578214</v>
+        <v>577946</v>
       </c>
       <c r="R41" t="n">
-        <v>7084276</v>
+        <v>7084330</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428424</v>
+        <v>125428359</v>
       </c>
       <c r="B7" t="n">
-        <v>56828</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578119</v>
+        <v>578081</v>
       </c>
       <c r="R7" t="n">
-        <v>7084345</v>
+        <v>7084315</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428381</v>
+        <v>125428424</v>
       </c>
       <c r="B8" t="n">
-        <v>78684</v>
+        <v>56828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,34 +1307,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578011</v>
+        <v>578119</v>
       </c>
       <c r="R8" t="n">
-        <v>7084346</v>
+        <v>7084345</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428359</v>
+        <v>125428381</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>78684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578081</v>
+        <v>578011</v>
       </c>
       <c r="R9" t="n">
-        <v>7084315</v>
+        <v>7084346</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125434423</v>
+        <v>125428427</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>91326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578129</v>
+        <v>577975</v>
       </c>
       <c r="R14" t="n">
-        <v>7084328</v>
+        <v>7084314</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1998,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428427</v>
+        <v>125428409</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2026,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577975</v>
+        <v>578221</v>
       </c>
       <c r="R15" t="n">
-        <v>7084314</v>
+        <v>7084280</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2112,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428409</v>
+        <v>125434423</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,42 +2128,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578221</v>
+        <v>578129</v>
       </c>
       <c r="R16" t="n">
-        <v>7084280</v>
+        <v>7084328</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2206,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428410</v>
+        <v>125428426</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>91326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3375,38 +3375,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578214</v>
+        <v>577942</v>
       </c>
       <c r="R28" t="n">
-        <v>7084276</v>
+        <v>7084344</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3465,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428426</v>
+        <v>125428410</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3481,34 +3477,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577942</v>
+        <v>578214</v>
       </c>
       <c r="R29" t="n">
-        <v>7084344</v>
+        <v>7084276</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125434411</v>
+        <v>125428384</v>
       </c>
       <c r="B2" t="n">
-        <v>78683</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578199</v>
+        <v>578310</v>
       </c>
       <c r="R2" t="n">
-        <v>7084408</v>
+        <v>7084391</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125434422</v>
+        <v>125428435</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578121</v>
+        <v>577974</v>
       </c>
       <c r="R3" t="n">
-        <v>7084311</v>
+        <v>7084344</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428384</v>
+        <v>125428440</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578310</v>
+        <v>578180</v>
       </c>
       <c r="R4" t="n">
-        <v>7084391</v>
+        <v>7084369</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428422</v>
+        <v>125428355</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577974</v>
+        <v>577852</v>
       </c>
       <c r="R5" t="n">
-        <v>7084348</v>
+        <v>7084241</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428386</v>
+        <v>125428407</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1095,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578323</v>
+        <v>578118</v>
       </c>
       <c r="R6" t="n">
-        <v>7084369</v>
+        <v>7084300</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428359</v>
+        <v>125434420</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578081</v>
+        <v>578025</v>
       </c>
       <c r="R7" t="n">
-        <v>7084315</v>
+        <v>7084331</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1279,22 +1279,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428424</v>
+        <v>125428386</v>
       </c>
       <c r="B8" t="n">
-        <v>56828</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,39 +1307,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578119</v>
+        <v>578323</v>
       </c>
       <c r="R8" t="n">
-        <v>7084345</v>
+        <v>7084369</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428381</v>
+        <v>125428359</v>
       </c>
       <c r="B9" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578011</v>
+        <v>578081</v>
       </c>
       <c r="R9" t="n">
-        <v>7084346</v>
+        <v>7084315</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428440</v>
+        <v>125428410</v>
       </c>
       <c r="B10" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,38 +1507,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578180</v>
+        <v>578214</v>
       </c>
       <c r="R10" t="n">
-        <v>7084369</v>
+        <v>7084276</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125434421</v>
+        <v>125428424</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>56828</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,34 +1617,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578083</v>
+        <v>578119</v>
       </c>
       <c r="R11" t="n">
-        <v>7084291</v>
+        <v>7084345</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1692,22 +1696,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428433</v>
+        <v>125428400</v>
       </c>
       <c r="B12" t="n">
-        <v>92448</v>
+        <v>78683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1720,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578080</v>
+        <v>577946</v>
       </c>
       <c r="R12" t="n">
-        <v>7084336</v>
+        <v>7084330</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125434420</v>
+        <v>125434411</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578025</v>
+        <v>578199</v>
       </c>
       <c r="R13" t="n">
-        <v>7084331</v>
+        <v>7084408</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428427</v>
+        <v>125428352</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>79565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1924,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577975</v>
+        <v>578226</v>
       </c>
       <c r="R14" t="n">
-        <v>7084314</v>
+        <v>7084292</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428409</v>
+        <v>125428403</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,42 +2026,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578221</v>
+        <v>578219</v>
       </c>
       <c r="R15" t="n">
-        <v>7084280</v>
+        <v>7084292</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125434423</v>
+        <v>125434406</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578129</v>
+        <v>578054</v>
       </c>
       <c r="R16" t="n">
-        <v>7084328</v>
+        <v>7084281</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428439</v>
+        <v>125434424</v>
       </c>
       <c r="B17" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578198</v>
+        <v>578129</v>
       </c>
       <c r="R17" t="n">
-        <v>7084409</v>
+        <v>7084335</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2308,19 +2308,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428435</v>
+        <v>125428433</v>
       </c>
       <c r="B18" t="n">
         <v>92448</v>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577974</v>
+        <v>578080</v>
       </c>
       <c r="R18" t="n">
-        <v>7084344</v>
+        <v>7084336</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428401</v>
+        <v>125428423</v>
       </c>
       <c r="B20" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,38 +2546,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577984</v>
+        <v>577989</v>
       </c>
       <c r="R20" t="n">
-        <v>7084342</v>
+        <v>7084344</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428423</v>
+        <v>125428409</v>
       </c>
       <c r="B21" t="n">
         <v>98269</v>
@@ -2671,7 +2675,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577989</v>
+        <v>578221</v>
       </c>
       <c r="R21" t="n">
-        <v>7084344</v>
+        <v>7084280</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2742,10 +2746,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428349</v>
+        <v>125428365</v>
       </c>
       <c r="B22" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2758,21 +2762,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2786,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578141</v>
+        <v>577840</v>
       </c>
       <c r="R22" t="n">
-        <v>7084345</v>
+        <v>7084230</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2844,10 +2848,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434424</v>
+        <v>125428402</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2860,21 +2864,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2884,10 +2888,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578129</v>
+        <v>578297</v>
       </c>
       <c r="R23" t="n">
-        <v>7084335</v>
+        <v>7084334</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2934,22 +2938,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428437</v>
+        <v>125434421</v>
       </c>
       <c r="B24" t="n">
-        <v>78331</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2962,21 +2966,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2986,10 +2990,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578117</v>
+        <v>578083</v>
       </c>
       <c r="R24" t="n">
-        <v>7084345</v>
+        <v>7084291</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3030,29 +3034,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125434406</v>
+        <v>125434422</v>
       </c>
       <c r="B25" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,21 +3068,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,10 +3092,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578054</v>
+        <v>578121</v>
       </c>
       <c r="R25" t="n">
-        <v>7084281</v>
+        <v>7084311</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,10 +3154,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428407</v>
+        <v>125428391</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,42 +3166,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578118</v>
+        <v>578310</v>
       </c>
       <c r="R26" t="n">
-        <v>7084300</v>
+        <v>7084392</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3257,10 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428391</v>
+        <v>125428422</v>
       </c>
       <c r="B27" t="n">
-        <v>80064</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,38 +3268,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578310</v>
+        <v>577974</v>
       </c>
       <c r="R27" t="n">
-        <v>7084392</v>
+        <v>7084348</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3359,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428426</v>
+        <v>125428349</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>75025</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,25 +3374,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577942</v>
+        <v>578141</v>
       </c>
       <c r="R28" t="n">
-        <v>7084344</v>
+        <v>7084345</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3461,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428410</v>
+        <v>125428439</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3473,42 +3476,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578214</v>
+        <v>578198</v>
       </c>
       <c r="R29" t="n">
-        <v>7084276</v>
+        <v>7084409</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3567,7 +3566,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125428403</v>
+        <v>125434410</v>
       </c>
       <c r="B30" t="n">
         <v>78683</v>
@@ -3607,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578219</v>
+        <v>578022</v>
       </c>
       <c r="R30" t="n">
-        <v>7084292</v>
+        <v>7084327</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3657,22 +3656,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428365</v>
+        <v>125428401</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>78683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3685,21 +3684,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3709,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577840</v>
+        <v>577984</v>
       </c>
       <c r="R31" t="n">
-        <v>7084230</v>
+        <v>7084342</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3771,7 +3770,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434410</v>
+        <v>125434407</v>
       </c>
       <c r="B32" t="n">
         <v>78683</v>
@@ -3811,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578022</v>
+        <v>577930</v>
       </c>
       <c r="R32" t="n">
-        <v>7084327</v>
+        <v>7084334</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3873,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428358</v>
+        <v>125434423</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3913,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578013</v>
+        <v>578129</v>
       </c>
       <c r="R33" t="n">
-        <v>7084338</v>
+        <v>7084328</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3963,22 +3962,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428355</v>
+        <v>125434408</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,21 +3990,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577852</v>
+        <v>577968</v>
       </c>
       <c r="R34" t="n">
-        <v>7084241</v>
+        <v>7084350</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4065,22 +4064,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428393</v>
+        <v>125428358</v>
       </c>
       <c r="B35" t="n">
-        <v>91636</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4093,21 +4092,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5467</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578033</v>
+        <v>578013</v>
       </c>
       <c r="R35" t="n">
-        <v>7084326</v>
+        <v>7084338</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4179,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125434407</v>
+        <v>125428380</v>
       </c>
       <c r="B36" t="n">
-        <v>78683</v>
+        <v>80056</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4191,25 +4190,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4219,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577930</v>
+        <v>577982</v>
       </c>
       <c r="R36" t="n">
-        <v>7084334</v>
+        <v>7084332</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4263,28 +4262,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428352</v>
+        <v>125428381</v>
       </c>
       <c r="B37" t="n">
-        <v>79565</v>
+        <v>78684</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578226</v>
+        <v>578011</v>
       </c>
       <c r="R37" t="n">
-        <v>7084292</v>
+        <v>7084346</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428402</v>
+        <v>125428426</v>
       </c>
       <c r="B38" t="n">
-        <v>78683</v>
+        <v>91326</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4395,25 +4395,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578297</v>
+        <v>577942</v>
       </c>
       <c r="R38" t="n">
-        <v>7084334</v>
+        <v>7084344</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428380</v>
+        <v>125428393</v>
       </c>
       <c r="B39" t="n">
-        <v>80056</v>
+        <v>91636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4497,25 +4497,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>5467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577982</v>
+        <v>578033</v>
       </c>
       <c r="R39" t="n">
-        <v>7084332</v>
+        <v>7084326</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4569,7 +4569,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4588,10 +4587,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125434408</v>
+        <v>125428437</v>
       </c>
       <c r="B40" t="n">
-        <v>78683</v>
+        <v>78331</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4604,21 +4603,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4628,10 +4627,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577968</v>
+        <v>578117</v>
       </c>
       <c r="R40" t="n">
-        <v>7084350</v>
+        <v>7084345</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4672,28 +4671,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428400</v>
+        <v>125428427</v>
       </c>
       <c r="B41" t="n">
-        <v>78683</v>
+        <v>91326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577946</v>
+        <v>577975</v>
       </c>
       <c r="R41" t="n">
-        <v>7084330</v>
+        <v>7084314</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428423</v>
+        <v>125428402</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,42 +2546,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577989</v>
+        <v>578297</v>
       </c>
       <c r="R20" t="n">
-        <v>7084344</v>
+        <v>7084334</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2640,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428409</v>
+        <v>125428365</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,42 +2648,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578221</v>
+        <v>577840</v>
       </c>
       <c r="R21" t="n">
-        <v>7084280</v>
+        <v>7084230</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2746,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428365</v>
+        <v>125428423</v>
       </c>
       <c r="B22" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2758,38 +2750,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577840</v>
+        <v>577989</v>
       </c>
       <c r="R22" t="n">
-        <v>7084230</v>
+        <v>7084344</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2848,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428402</v>
+        <v>125428409</v>
       </c>
       <c r="B23" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2860,38 +2856,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578297</v>
+        <v>578221</v>
       </c>
       <c r="R23" t="n">
-        <v>7084334</v>
+        <v>7084280</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428422</v>
+        <v>125428349</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
+        <v>75025</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3268,42 +3268,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577974</v>
+        <v>578141</v>
       </c>
       <c r="R27" t="n">
-        <v>7084348</v>
+        <v>7084345</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3362,10 +3358,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428349</v>
+        <v>125428422</v>
       </c>
       <c r="B28" t="n">
-        <v>75025</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3374,38 +3370,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578141</v>
+        <v>577974</v>
       </c>
       <c r="R28" t="n">
-        <v>7084345</v>
+        <v>7084348</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -3256,10 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428349</v>
+        <v>125428422</v>
       </c>
       <c r="B27" t="n">
-        <v>75025</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3268,38 +3268,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578141</v>
+        <v>577974</v>
       </c>
       <c r="R27" t="n">
-        <v>7084345</v>
+        <v>7084348</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3358,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428422</v>
+        <v>125428349</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>75025</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3370,42 +3374,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577974</v>
+        <v>578141</v>
       </c>
       <c r="R28" t="n">
-        <v>7084348</v>
+        <v>7084345</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428384</v>
+        <v>125428349</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578310</v>
+        <v>578141</v>
       </c>
       <c r="R2" t="n">
-        <v>7084391</v>
+        <v>7084345</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,40 +772,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428435</v>
+        <v>125428422</v>
       </c>
       <c r="B3" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
@@ -820,7 +814,7 @@
         <v>577974</v>
       </c>
       <c r="R3" t="n">
-        <v>7084344</v>
+        <v>7084348</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,50 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428440</v>
+        <v>125428407</v>
       </c>
       <c r="B4" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578180</v>
+        <v>578118</v>
       </c>
       <c r="R4" t="n">
-        <v>7084369</v>
+        <v>7084300</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428355</v>
+        <v>125428393</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577852</v>
+        <v>578033</v>
       </c>
       <c r="R5" t="n">
-        <v>7084241</v>
+        <v>7084326</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,54 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428407</v>
+        <v>125434411</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578118</v>
+        <v>578199</v>
       </c>
       <c r="R6" t="n">
-        <v>7084300</v>
+        <v>7084408</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1177,49 +1156,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125434420</v>
+        <v>125428391</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578025</v>
+        <v>578310</v>
       </c>
       <c r="R7" t="n">
-        <v>7084331</v>
+        <v>7084392</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1279,27 +1253,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125428386</v>
+        <v>125428438</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,34 +1276,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578323</v>
+        <v>578202</v>
       </c>
       <c r="R8" t="n">
-        <v>7084369</v>
+        <v>7084386</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1367,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,37 +1372,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428359</v>
+        <v>125428435</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578081</v>
+        <v>577974</v>
       </c>
       <c r="R9" t="n">
-        <v>7084315</v>
+        <v>7084344</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428410</v>
+        <v>125428426</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,38 +1480,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578214</v>
+        <v>577942</v>
       </c>
       <c r="R10" t="n">
-        <v>7084276</v>
+        <v>7084344</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428424</v>
+        <v>125428359</v>
       </c>
       <c r="B11" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,39 +1577,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578119</v>
+        <v>578081</v>
       </c>
       <c r="R11" t="n">
-        <v>7084345</v>
+        <v>7084315</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,50 +1663,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428400</v>
+        <v>125428410</v>
       </c>
       <c r="B12" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577946</v>
+        <v>578214</v>
       </c>
       <c r="R12" t="n">
-        <v>7084330</v>
+        <v>7084276</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,15 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125434411</v>
+        <v>125428352</v>
       </c>
       <c r="B13" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,21 +1775,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578199</v>
+        <v>578226</v>
       </c>
       <c r="R13" t="n">
-        <v>7084408</v>
+        <v>7084292</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1900,27 +1849,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428352</v>
+        <v>125434406</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1872,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578226</v>
+        <v>578054</v>
       </c>
       <c r="R14" t="n">
-        <v>7084292</v>
+        <v>7084281</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2002,27 +1946,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125428403</v>
+        <v>125428439</v>
       </c>
       <c r="B15" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,10 +1993,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578219</v>
+        <v>578198</v>
       </c>
       <c r="R15" t="n">
-        <v>7084292</v>
+        <v>7084409</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,15 +2055,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125434406</v>
+        <v>125434407</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2066,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578054</v>
+        <v>577930</v>
       </c>
       <c r="R16" t="n">
-        <v>7084281</v>
+        <v>7084334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,15 +2152,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125434424</v>
+        <v>125428403</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2234,21 +2163,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578129</v>
+        <v>578219</v>
       </c>
       <c r="R17" t="n">
-        <v>7084335</v>
+        <v>7084292</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2308,49 +2237,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125428433</v>
+        <v>125428358</v>
       </c>
       <c r="B18" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2360,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578080</v>
+        <v>578013</v>
       </c>
       <c r="R18" t="n">
-        <v>7084336</v>
+        <v>7084338</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2422,15 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125428438</v>
+        <v>125428355</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,39 +2357,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578202</v>
+        <v>577852</v>
       </c>
       <c r="R19" t="n">
-        <v>7084386</v>
+        <v>7084241</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2503,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,15 +2443,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125428402</v>
+        <v>125428400</v>
       </c>
       <c r="B20" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578297</v>
+        <v>577946</v>
       </c>
       <c r="R20" t="n">
-        <v>7084334</v>
+        <v>7084330</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,15 +2540,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125428365</v>
+        <v>125434422</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,21 +2551,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577840</v>
+        <v>578121</v>
       </c>
       <c r="R21" t="n">
-        <v>7084230</v>
+        <v>7084311</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,27 +2625,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428423</v>
+        <v>125428427</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,38 +2648,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577989</v>
+        <v>577975</v>
       </c>
       <c r="R22" t="n">
-        <v>7084344</v>
+        <v>7084314</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2844,54 +2734,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428409</v>
+        <v>125434421</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578221</v>
+        <v>578083</v>
       </c>
       <c r="R23" t="n">
-        <v>7084280</v>
+        <v>7084291</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2938,27 +2819,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125434421</v>
+        <v>125428365</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2966,21 +2842,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2990,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578083</v>
+        <v>577840</v>
       </c>
       <c r="R24" t="n">
-        <v>7084291</v>
+        <v>7084230</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3040,27 +2916,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125434422</v>
+        <v>125434423</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578121</v>
+        <v>578129</v>
       </c>
       <c r="R25" t="n">
-        <v>7084311</v>
+        <v>7084328</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3154,37 +3025,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428391</v>
+        <v>125434408</v>
       </c>
       <c r="B26" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3060,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578310</v>
+        <v>577968</v>
       </c>
       <c r="R26" t="n">
-        <v>7084392</v>
+        <v>7084350</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3244,66 +3110,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428422</v>
+        <v>125434420</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577974</v>
+        <v>578025</v>
       </c>
       <c r="R27" t="n">
-        <v>7084348</v>
+        <v>7084331</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3350,62 +3207,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428349</v>
+        <v>125428423</v>
       </c>
       <c r="B28" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578141</v>
+        <v>577989</v>
       </c>
       <c r="R28" t="n">
-        <v>7084345</v>
+        <v>7084344</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3464,50 +3320,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125428439</v>
+        <v>125428409</v>
       </c>
       <c r="B29" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578198</v>
+        <v>578221</v>
       </c>
       <c r="R29" t="n">
-        <v>7084409</v>
+        <v>7084280</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3566,15 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125434410</v>
+        <v>125434424</v>
       </c>
       <c r="B30" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578022</v>
+        <v>578129</v>
       </c>
       <c r="R30" t="n">
-        <v>7084327</v>
+        <v>7084335</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3668,37 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125428401</v>
+        <v>125428380</v>
       </c>
       <c r="B31" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577984</v>
+        <v>577982</v>
       </c>
       <c r="R31" t="n">
-        <v>7084342</v>
+        <v>7084332</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3752,6 +3597,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3770,15 +3616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125434407</v>
+        <v>125428384</v>
       </c>
       <c r="B32" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3786,21 +3627,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3651,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577930</v>
+        <v>578310</v>
       </c>
       <c r="R32" t="n">
-        <v>7084334</v>
+        <v>7084391</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3860,27 +3701,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125434423</v>
+        <v>125428437</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,21 +3724,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578129</v>
+        <v>578117</v>
       </c>
       <c r="R33" t="n">
-        <v>7084328</v>
+        <v>7084345</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3956,33 +3792,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125434408</v>
+        <v>125428424</v>
       </c>
       <c r="B34" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3990,34 +3822,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577968</v>
+        <v>578119</v>
       </c>
       <c r="R34" t="n">
-        <v>7084350</v>
+        <v>7084345</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4064,27 +3901,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428358</v>
+        <v>125428381</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4092,21 +3924,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4116,10 +3948,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578013</v>
+        <v>578011</v>
       </c>
       <c r="R35" t="n">
-        <v>7084338</v>
+        <v>7084346</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4178,37 +4010,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428380</v>
+        <v>125428440</v>
       </c>
       <c r="B36" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577982</v>
+        <v>578180</v>
       </c>
       <c r="R36" t="n">
-        <v>7084332</v>
+        <v>7084369</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4262,7 +4089,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4281,15 +4107,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125428381</v>
+        <v>125428402</v>
       </c>
       <c r="B37" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,21 +4118,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4142,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578011</v>
+        <v>578297</v>
       </c>
       <c r="R37" t="n">
-        <v>7084346</v>
+        <v>7084334</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4383,37 +4204,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125428426</v>
+        <v>125428433</v>
       </c>
       <c r="B38" t="n">
-        <v>91326</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4423,10 +4239,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577942</v>
+        <v>578080</v>
       </c>
       <c r="R38" t="n">
-        <v>7084344</v>
+        <v>7084336</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4485,15 +4301,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125428393</v>
+        <v>125428401</v>
       </c>
       <c r="B39" t="n">
-        <v>91636</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4501,21 +4312,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5467</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4525,10 +4336,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578033</v>
+        <v>577984</v>
       </c>
       <c r="R39" t="n">
-        <v>7084326</v>
+        <v>7084342</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4587,15 +4398,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125428437</v>
+        <v>125428386</v>
       </c>
       <c r="B40" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,21 +4409,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4627,10 +4433,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578117</v>
+        <v>578323</v>
       </c>
       <c r="R40" t="n">
-        <v>7084345</v>
+        <v>7084369</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4671,7 +4477,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4690,37 +4495,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125428427</v>
+        <v>125434410</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4730,10 +4530,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577975</v>
+        <v>578022</v>
       </c>
       <c r="R41" t="n">
-        <v>7084314</v>
+        <v>7084327</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4780,15 +4580,121 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125825795</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91502</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>71</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skirsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>578002</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7084345</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Mikroskopierad</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428349</v>
+        <v>125428422</v>
       </c>
       <c r="B2" t="n">
-        <v>75066</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578141</v>
+        <v>577974</v>
       </c>
       <c r="R2" t="n">
-        <v>7084345</v>
+        <v>7084348</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428422</v>
+        <v>125428349</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>75066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577974</v>
+        <v>578141</v>
       </c>
       <c r="R3" t="n">
-        <v>7084348</v>
+        <v>7084345</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +876,7 @@
         <v>125428407</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125428393</v>
       </c>
       <c r="B5" t="n">
-        <v>91690</v>
+        <v>91697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1372,32 +1372,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428435</v>
+        <v>125428426</v>
       </c>
       <c r="B9" t="n">
-        <v>92502</v>
+        <v>91387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577974</v>
+        <v>577942</v>
       </c>
       <c r="R9" t="n">
         <v>7084344</v>
@@ -1469,32 +1469,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428426</v>
+        <v>125428435</v>
       </c>
       <c r="B10" t="n">
-        <v>91380</v>
+        <v>92509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577942</v>
+        <v>577974</v>
       </c>
       <c r="R10" t="n">
         <v>7084344</v>
@@ -1666,7 +1666,7 @@
         <v>125428410</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2637,32 +2637,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428427</v>
+        <v>125434421</v>
       </c>
       <c r="B22" t="n">
-        <v>91380</v>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577975</v>
+        <v>578083</v>
       </c>
       <c r="R22" t="n">
-        <v>7084314</v>
+        <v>7084291</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,19 +2722,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434421</v>
+        <v>125434423</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578083</v>
+        <v>578129</v>
       </c>
       <c r="R23" t="n">
-        <v>7084291</v>
+        <v>7084328</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2834,7 +2834,7 @@
         <v>125428365</v>
       </c>
       <c r="B24" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,32 +2928,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125434423</v>
+        <v>125428427</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>91387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578129</v>
+        <v>577975</v>
       </c>
       <c r="R25" t="n">
-        <v>7084328</v>
+        <v>7084314</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,12 +3013,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         <v>125428423</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>125428409</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428424</v>
+        <v>125428381</v>
       </c>
       <c r="B34" t="n">
-        <v>56834</v>
+        <v>78726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,39 +3822,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578119</v>
+        <v>578011</v>
       </c>
       <c r="R34" t="n">
-        <v>7084345</v>
+        <v>7084346</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3913,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428381</v>
+        <v>125428440</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>78725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3924,21 +3919,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3948,10 +3943,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578011</v>
+        <v>578180</v>
       </c>
       <c r="R35" t="n">
-        <v>7084346</v>
+        <v>7084369</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428440</v>
+        <v>125428424</v>
       </c>
       <c r="B36" t="n">
-        <v>78725</v>
+        <v>56834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4021,34 +4016,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578180</v>
+        <v>578119</v>
       </c>
       <c r="R36" t="n">
-        <v>7084369</v>
+        <v>7084345</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4207,7 +4207,7 @@
         <v>125428433</v>
       </c>
       <c r="B38" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91502</v>
+        <v>91509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428422</v>
+        <v>125428349</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>75066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577974</v>
+        <v>578141</v>
       </c>
       <c r="R2" t="n">
-        <v>7084348</v>
+        <v>7084345</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -776,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428349</v>
+        <v>125428407</v>
       </c>
       <c r="B3" t="n">
-        <v>75066</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578141</v>
+        <v>578118</v>
       </c>
       <c r="R3" t="n">
-        <v>7084345</v>
+        <v>7084300</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428407</v>
+        <v>125428422</v>
       </c>
       <c r="B4" t="n">
         <v>98331</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578118</v>
+        <v>577974</v>
       </c>
       <c r="R4" t="n">
-        <v>7084300</v>
+        <v>7084348</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428440</v>
+        <v>125428424</v>
       </c>
       <c r="B35" t="n">
-        <v>78725</v>
+        <v>56834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,34 +3919,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578180</v>
+        <v>578119</v>
       </c>
       <c r="R35" t="n">
-        <v>7084369</v>
+        <v>7084345</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4005,10 +4010,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428424</v>
+        <v>125428440</v>
       </c>
       <c r="B36" t="n">
-        <v>56834</v>
+        <v>78725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4016,39 +4021,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578119</v>
+        <v>578180</v>
       </c>
       <c r="R36" t="n">
-        <v>7084345</v>
+        <v>7084369</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91509</v>
+        <v>91510</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125428349</v>
       </c>
       <c r="B2" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428407</v>
+        <v>125428422</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578118</v>
+        <v>577974</v>
       </c>
       <c r="R3" t="n">
-        <v>7084300</v>
+        <v>7084348</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428422</v>
+        <v>125428407</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577974</v>
+        <v>578118</v>
       </c>
       <c r="R4" t="n">
-        <v>7084348</v>
+        <v>7084300</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428393</v>
+        <v>125428391</v>
       </c>
       <c r="B5" t="n">
-        <v>91697</v>
+        <v>80107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5467</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578033</v>
+        <v>578310</v>
       </c>
       <c r="R5" t="n">
-        <v>7084326</v>
+        <v>7084392</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>125434411</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428391</v>
+        <v>125428393</v>
       </c>
       <c r="B7" t="n">
-        <v>80106</v>
+        <v>91701</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>5467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578310</v>
+        <v>578033</v>
       </c>
       <c r="R7" t="n">
-        <v>7084392</v>
+        <v>7084326</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1372,32 +1372,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428426</v>
+        <v>125428359</v>
       </c>
       <c r="B9" t="n">
-        <v>91387</v>
+        <v>79586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577942</v>
+        <v>578081</v>
       </c>
       <c r="R9" t="n">
-        <v>7084344</v>
+        <v>7084315</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1469,32 +1469,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428435</v>
+        <v>125428426</v>
       </c>
       <c r="B10" t="n">
-        <v>92509</v>
+        <v>91389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577974</v>
+        <v>577942</v>
       </c>
       <c r="R10" t="n">
         <v>7084344</v>
@@ -1566,32 +1566,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428359</v>
+        <v>125428435</v>
       </c>
       <c r="B11" t="n">
-        <v>79585</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578081</v>
+        <v>577974</v>
       </c>
       <c r="R11" t="n">
-        <v>7084315</v>
+        <v>7084344</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1666,7 +1666,7 @@
         <v>125428410</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428352</v>
+        <v>125434406</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578226</v>
+        <v>578054</v>
       </c>
       <c r="R13" t="n">
-        <v>7084292</v>
+        <v>7084281</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,22 +1849,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125434406</v>
+        <v>125428352</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578054</v>
+        <v>578226</v>
       </c>
       <c r="R14" t="n">
-        <v>7084281</v>
+        <v>7084292</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1946,12 +1946,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
         <v>125428439</v>
       </c>
       <c r="B15" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125434407</v>
+        <v>125428403</v>
       </c>
       <c r="B16" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577930</v>
+        <v>578219</v>
       </c>
       <c r="R16" t="n">
-        <v>7084334</v>
+        <v>7084292</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,22 +2140,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125428403</v>
+        <v>125434407</v>
       </c>
       <c r="B17" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578219</v>
+        <v>577930</v>
       </c>
       <c r="R17" t="n">
-        <v>7084292</v>
+        <v>7084334</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2237,12 +2237,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2252,7 +2252,7 @@
         <v>125428358</v>
       </c>
       <c r="B18" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>125428355</v>
       </c>
       <c r="B19" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>125428400</v>
       </c>
       <c r="B20" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>125434422</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125434421</v>
+        <v>125434423</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578083</v>
+        <v>578129</v>
       </c>
       <c r="R22" t="n">
-        <v>7084291</v>
+        <v>7084328</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434423</v>
+        <v>125434421</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578129</v>
+        <v>578083</v>
       </c>
       <c r="R23" t="n">
-        <v>7084328</v>
+        <v>7084291</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428365</v>
+        <v>125428427</v>
       </c>
       <c r="B24" t="n">
-        <v>91227</v>
+        <v>91389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577840</v>
+        <v>577975</v>
       </c>
       <c r="R24" t="n">
-        <v>7084230</v>
+        <v>7084314</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2928,32 +2928,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428427</v>
+        <v>125428365</v>
       </c>
       <c r="B25" t="n">
-        <v>91387</v>
+        <v>91228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577975</v>
+        <v>577840</v>
       </c>
       <c r="R25" t="n">
-        <v>7084314</v>
+        <v>7084230</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3025,45 +3025,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125434408</v>
+        <v>125428423</v>
       </c>
       <c r="B26" t="n">
-        <v>78725</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577968</v>
+        <v>577989</v>
       </c>
       <c r="R26" t="n">
-        <v>7084350</v>
+        <v>7084344</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3110,12 +3114,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3125,7 +3129,7 @@
         <v>125434420</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3219,49 +3223,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428423</v>
+        <v>125434408</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>78726</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577989</v>
+        <v>577968</v>
       </c>
       <c r="R28" t="n">
-        <v>7084344</v>
+        <v>7084350</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3308,12 +3308,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
         <v>125428409</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>125434424</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>125428380</v>
       </c>
       <c r="B31" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428384</v>
+        <v>125428437</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>78374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578310</v>
+        <v>578117</v>
       </c>
       <c r="R32" t="n">
-        <v>7084391</v>
+        <v>7084345</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3695,6 +3695,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3714,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428437</v>
+        <v>125428384</v>
       </c>
       <c r="B33" t="n">
-        <v>78373</v>
+        <v>80071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3724,21 +3725,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3748,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578117</v>
+        <v>578310</v>
       </c>
       <c r="R33" t="n">
-        <v>7084345</v>
+        <v>7084391</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,7 +3793,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>125428381</v>
       </c>
       <c r="B34" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428424</v>
+        <v>125428440</v>
       </c>
       <c r="B35" t="n">
-        <v>56834</v>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,39 +3919,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578119</v>
+        <v>578180</v>
       </c>
       <c r="R35" t="n">
-        <v>7084345</v>
+        <v>7084369</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428440</v>
+        <v>125428424</v>
       </c>
       <c r="B36" t="n">
-        <v>78725</v>
+        <v>56834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4021,34 +4016,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578180</v>
+        <v>578119</v>
       </c>
       <c r="R36" t="n">
-        <v>7084369</v>
+        <v>7084345</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
         <v>125428402</v>
       </c>
       <c r="B37" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>125428433</v>
       </c>
       <c r="B38" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>125428401</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>125428386</v>
       </c>
       <c r="B40" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>125434410</v>
       </c>
       <c r="B41" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91510</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -2637,32 +2637,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125434423</v>
+        <v>125428427</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>91389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578129</v>
+        <v>577975</v>
       </c>
       <c r="R22" t="n">
-        <v>7084328</v>
+        <v>7084314</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,22 +2722,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434421</v>
+        <v>125428365</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>91228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2745,21 +2745,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578083</v>
+        <v>577840</v>
       </c>
       <c r="R23" t="n">
-        <v>7084291</v>
+        <v>7084230</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2819,44 +2819,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428427</v>
+        <v>125434423</v>
       </c>
       <c r="B24" t="n">
-        <v>91389</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577975</v>
+        <v>578129</v>
       </c>
       <c r="R24" t="n">
-        <v>7084314</v>
+        <v>7084328</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2916,22 +2916,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428365</v>
+        <v>125434421</v>
       </c>
       <c r="B25" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2939,21 +2939,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577840</v>
+        <v>578083</v>
       </c>
       <c r="R25" t="n">
-        <v>7084230</v>
+        <v>7084291</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,12 +3013,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428381</v>
+        <v>125428440</v>
       </c>
       <c r="B34" t="n">
-        <v>78727</v>
+        <v>78726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578011</v>
+        <v>578180</v>
       </c>
       <c r="R34" t="n">
-        <v>7084346</v>
+        <v>7084369</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428440</v>
+        <v>125428424</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>56834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,34 +3919,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578180</v>
+        <v>578119</v>
       </c>
       <c r="R35" t="n">
-        <v>7084369</v>
+        <v>7084345</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4005,10 +4010,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428424</v>
+        <v>125428381</v>
       </c>
       <c r="B36" t="n">
-        <v>56834</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4016,39 +4021,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578119</v>
+        <v>578011</v>
       </c>
       <c r="R36" t="n">
-        <v>7084345</v>
+        <v>7084346</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125428422</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>125428407</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125428391</v>
+        <v>125434411</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578310</v>
+        <v>578199</v>
       </c>
       <c r="R5" t="n">
-        <v>7084392</v>
+        <v>7084408</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,22 +1059,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125434411</v>
+        <v>125428393</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>91705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578199</v>
+        <v>578033</v>
       </c>
       <c r="R6" t="n">
-        <v>7084408</v>
+        <v>7084326</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,44 +1156,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428393</v>
+        <v>125428391</v>
       </c>
       <c r="B7" t="n">
-        <v>91701</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5467</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578033</v>
+        <v>578310</v>
       </c>
       <c r="R7" t="n">
-        <v>7084326</v>
+        <v>7084392</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1372,45 +1372,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428359</v>
+        <v>125428410</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578081</v>
+        <v>578214</v>
       </c>
       <c r="R9" t="n">
-        <v>7084315</v>
+        <v>7084276</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1472,7 +1476,7 @@
         <v>125428426</v>
       </c>
       <c r="B10" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,32 +1570,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428435</v>
+        <v>125428359</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577974</v>
+        <v>578081</v>
       </c>
       <c r="R11" t="n">
-        <v>7084344</v>
+        <v>7084315</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1663,49 +1667,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428410</v>
+        <v>125428435</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578214</v>
+        <v>577974</v>
       </c>
       <c r="R12" t="n">
-        <v>7084276</v>
+        <v>7084344</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125434406</v>
+        <v>125428352</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578054</v>
+        <v>578226</v>
       </c>
       <c r="R13" t="n">
-        <v>7084281</v>
+        <v>7084292</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,22 +1849,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428352</v>
+        <v>125434406</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578226</v>
+        <v>578054</v>
       </c>
       <c r="R14" t="n">
-        <v>7084292</v>
+        <v>7084281</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1946,12 +1946,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
         <v>125428439</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>125428403</v>
       </c>
       <c r="B16" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>125434407</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>125428358</v>
       </c>
       <c r="B18" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>125428355</v>
       </c>
       <c r="B19" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>125428400</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>125434422</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>125428427</v>
       </c>
       <c r="B22" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125428365</v>
+        <v>125434423</v>
       </c>
       <c r="B23" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2745,21 +2745,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577840</v>
+        <v>578129</v>
       </c>
       <c r="R23" t="n">
-        <v>7084230</v>
+        <v>7084328</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2819,22 +2819,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125434423</v>
+        <v>125434421</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578129</v>
+        <v>578083</v>
       </c>
       <c r="R24" t="n">
-        <v>7084328</v>
+        <v>7084291</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125434421</v>
+        <v>125428365</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>91232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2939,21 +2939,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578083</v>
+        <v>577840</v>
       </c>
       <c r="R25" t="n">
-        <v>7084291</v>
+        <v>7084230</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,12 +3013,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3028,7 +3028,7 @@
         <v>125428423</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>125434420</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>125434408</v>
       </c>
       <c r="B28" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>125428409</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>125434424</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>125428380</v>
       </c>
       <c r="B31" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>125428437</v>
       </c>
       <c r="B32" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125428384</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125428440</v>
+        <v>125428381</v>
       </c>
       <c r="B34" t="n">
-        <v>78726</v>
+        <v>78731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578180</v>
+        <v>578011</v>
       </c>
       <c r="R34" t="n">
-        <v>7084369</v>
+        <v>7084346</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125428424</v>
+        <v>125428440</v>
       </c>
       <c r="B35" t="n">
-        <v>56834</v>
+        <v>78730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3919,39 +3919,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578119</v>
+        <v>578180</v>
       </c>
       <c r="R35" t="n">
-        <v>7084345</v>
+        <v>7084369</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125428381</v>
+        <v>125428424</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>56834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4021,34 +4016,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578011</v>
+        <v>578119</v>
       </c>
       <c r="R36" t="n">
-        <v>7084346</v>
+        <v>7084345</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
         <v>125428402</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>125428433</v>
       </c>
       <c r="B38" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>125428401</v>
       </c>
       <c r="B39" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>125428386</v>
       </c>
       <c r="B40" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>125434410</v>
       </c>
       <c r="B41" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91513</v>
+        <v>91517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -1570,32 +1570,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428359</v>
+        <v>125428435</v>
       </c>
       <c r="B11" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578081</v>
+        <v>577974</v>
       </c>
       <c r="R11" t="n">
-        <v>7084315</v>
+        <v>7084344</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428435</v>
+        <v>125428359</v>
       </c>
       <c r="B12" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577974</v>
+        <v>578081</v>
       </c>
       <c r="R12" t="n">
-        <v>7084344</v>
+        <v>7084315</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2637,32 +2637,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125428427</v>
+        <v>125434423</v>
       </c>
       <c r="B22" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577975</v>
+        <v>578129</v>
       </c>
       <c r="R22" t="n">
-        <v>7084314</v>
+        <v>7084328</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,19 +2722,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125434423</v>
+        <v>125434421</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578129</v>
+        <v>578083</v>
       </c>
       <c r="R23" t="n">
-        <v>7084328</v>
+        <v>7084291</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125434421</v>
+        <v>125428427</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578083</v>
+        <v>577975</v>
       </c>
       <c r="R24" t="n">
-        <v>7084291</v>
+        <v>7084314</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2916,12 +2916,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125428422</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>125428407</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125428393</v>
+        <v>125428391</v>
       </c>
       <c r="B6" t="n">
-        <v>91705</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5467</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578033</v>
+        <v>578310</v>
       </c>
       <c r="R6" t="n">
-        <v>7084326</v>
+        <v>7084392</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125428391</v>
+        <v>125428393</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>91705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>5467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578310</v>
+        <v>578033</v>
       </c>
       <c r="R7" t="n">
-        <v>7084392</v>
+        <v>7084326</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1375,7 +1375,7 @@
         <v>125428410</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125428403</v>
+        <v>125434407</v>
       </c>
       <c r="B16" t="n">
         <v>78730</v>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578219</v>
+        <v>577930</v>
       </c>
       <c r="R16" t="n">
-        <v>7084292</v>
+        <v>7084334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,19 +2140,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125434407</v>
+        <v>125428403</v>
       </c>
       <c r="B17" t="n">
         <v>78730</v>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577930</v>
+        <v>578219</v>
       </c>
       <c r="R17" t="n">
-        <v>7084334</v>
+        <v>7084292</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2237,12 +2237,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125434423</v>
+        <v>125428365</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578129</v>
+        <v>577840</v>
       </c>
       <c r="R22" t="n">
-        <v>7084328</v>
+        <v>7084230</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,12 +2722,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125428427</v>
+        <v>125434423</v>
       </c>
       <c r="B24" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577975</v>
+        <v>578129</v>
       </c>
       <c r="R24" t="n">
-        <v>7084314</v>
+        <v>7084328</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2916,44 +2916,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125428365</v>
+        <v>125428427</v>
       </c>
       <c r="B25" t="n">
-        <v>91232</v>
+        <v>91393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577840</v>
+        <v>577975</v>
       </c>
       <c r="R25" t="n">
-        <v>7084230</v>
+        <v>7084314</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3025,49 +3025,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125428423</v>
+        <v>125434420</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577989</v>
+        <v>578025</v>
       </c>
       <c r="R26" t="n">
-        <v>7084344</v>
+        <v>7084331</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3114,57 +3110,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125434420</v>
+        <v>125428423</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578025</v>
+        <v>577989</v>
       </c>
       <c r="R27" t="n">
-        <v>7084331</v>
+        <v>7084344</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3211,12 +3211,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
         <v>125428409</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125428437</v>
+        <v>125428384</v>
       </c>
       <c r="B32" t="n">
-        <v>78378</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578117</v>
+        <v>578310</v>
       </c>
       <c r="R32" t="n">
-        <v>7084345</v>
+        <v>7084391</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3695,7 +3695,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3714,10 +3713,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125428384</v>
+        <v>125428437</v>
       </c>
       <c r="B33" t="n">
-        <v>80075</v>
+        <v>78378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3725,21 +3724,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578310</v>
+        <v>578117</v>
       </c>
       <c r="R33" t="n">
-        <v>7084391</v>
+        <v>7084345</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3793,6 +3792,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -3025,10 +3025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125434420</v>
+        <v>125434408</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3036,21 +3036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578025</v>
+        <v>577968</v>
       </c>
       <c r="R26" t="n">
-        <v>7084331</v>
+        <v>7084350</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3122,49 +3122,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125428423</v>
+        <v>125434420</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577989</v>
+        <v>578025</v>
       </c>
       <c r="R27" t="n">
-        <v>7084344</v>
+        <v>7084331</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3211,57 +3207,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125434408</v>
+        <v>125428423</v>
       </c>
       <c r="B28" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577968</v>
+        <v>577989</v>
       </c>
       <c r="R28" t="n">
-        <v>7084350</v>
+        <v>7084344</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3308,12 +3308,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125428349</v>
+        <v>125428422</v>
       </c>
       <c r="B2" t="n">
-        <v>75067</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578141</v>
+        <v>577974</v>
       </c>
       <c r="R2" t="n">
-        <v>7084345</v>
+        <v>7084348</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125428422</v>
+        <v>125428407</v>
       </c>
       <c r="B3" t="n">
         <v>98339</v>
@@ -802,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -811,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577974</v>
+        <v>578118</v>
       </c>
       <c r="R3" t="n">
-        <v>7084348</v>
+        <v>7084300</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125428407</v>
+        <v>125428349</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>75067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578118</v>
+        <v>578141</v>
       </c>
       <c r="R4" t="n">
-        <v>7084300</v>
+        <v>7084345</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125428410</v>
+        <v>125428426</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>91393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,38 +1383,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578214</v>
+        <v>577942</v>
       </c>
       <c r="R9" t="n">
-        <v>7084276</v>
+        <v>7084344</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1473,32 +1469,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125428426</v>
+        <v>125428435</v>
       </c>
       <c r="B10" t="n">
-        <v>91393</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1508,7 +1504,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577942</v>
+        <v>577974</v>
       </c>
       <c r="R10" t="n">
         <v>7084344</v>
@@ -1570,32 +1566,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125428435</v>
+        <v>125428359</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577974</v>
+        <v>578081</v>
       </c>
       <c r="R11" t="n">
-        <v>7084344</v>
+        <v>7084315</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,45 +1663,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125428359</v>
+        <v>125428410</v>
       </c>
       <c r="B12" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578081</v>
+        <v>578214</v>
       </c>
       <c r="R12" t="n">
-        <v>7084315</v>
+        <v>7084276</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125434408</v>
+        <v>125434420</v>
       </c>
       <c r="B26" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3036,21 +3036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577968</v>
+        <v>578025</v>
       </c>
       <c r="R26" t="n">
-        <v>7084350</v>
+        <v>7084331</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3122,45 +3122,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125434420</v>
+        <v>125428423</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578025</v>
+        <v>577989</v>
       </c>
       <c r="R27" t="n">
-        <v>7084331</v>
+        <v>7084344</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3207,61 +3211,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125428423</v>
+        <v>125434408</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skirsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577989</v>
+        <v>577968</v>
       </c>
       <c r="R28" t="n">
-        <v>7084344</v>
+        <v>7084350</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3308,12 +3308,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91517</v>
+        <v>91519</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91519</v>
+        <v>91521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91521</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>91527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23630-2025 artfynd.xlsx
+++ b/artfynd/A 23630-2025 artfynd.xlsx
@@ -4595,7 +4595,7 @@
         <v>125825795</v>
       </c>
       <c r="B42" t="n">
-        <v>91527</v>
+        <v>91530</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
